--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8512,0.0769,0.0392,0.0305</t>
-  </si>
-  <si>
-    <t>0.0089,0.0011,0.0016,0.9950</t>
-  </si>
-  <si>
-    <t>0.8129,0.0034,0.0003,0.1743</t>
-  </si>
-  <si>
-    <t>0.0960,0.0144,0.0034,0.9518</t>
-  </si>
-  <si>
-    <t>0.9954,0.0028,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0014,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9962,0.0021,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9913,0.0064,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9945,0.0059,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9605,0.0544,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9926,0.0118,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0036,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.8492,0.0164,0.1664,0.0109</t>
-  </si>
-  <si>
-    <t>0.1793,0.2907,0.5524,0.0022</t>
-  </si>
-  <si>
-    <t>0.4847,0.0215,0.6614,0.0034</t>
-  </si>
-  <si>
-    <t>0.3510,0.0911,0.6223,0.0059</t>
-  </si>
-  <si>
-    <t>0.8805,0.0110,0.1422,0.0026</t>
-  </si>
-  <si>
-    <t>0.0108,0.9765,0.0322,0.0003</t>
-  </si>
-  <si>
-    <t>0.0175,0.9740,0.0129,0.0002</t>
-  </si>
-  <si>
-    <t>0.0500,0.9283,0.0380,0.0007</t>
-  </si>
-  <si>
-    <t>0.0372,0.9502,0.0183,0.0008</t>
-  </si>
-  <si>
-    <t>0.0040,0.9905,0.0130,0.0001</t>
-  </si>
-  <si>
-    <t>0.3517,0.0614,0.6445,0.0198</t>
-  </si>
-  <si>
-    <t>0.4624,0.0442,0.5724,0.0066</t>
-  </si>
-  <si>
-    <t>0.0158,0.0097,0.9777,0.0044</t>
-  </si>
-  <si>
-    <t>0.1610,0.0023,0.8064,0.0554</t>
-  </si>
-  <si>
-    <t>0.1229,0.0133,0.9089,0.0069</t>
-  </si>
-  <si>
-    <t>0.1200,0.0060,0.9166,0.0075</t>
-  </si>
-  <si>
-    <t>0.0305,0.0048,0.9819,0.0007</t>
-  </si>
-  <si>
-    <t>0.3584,0.7313,0.0057,0.0056</t>
-  </si>
-  <si>
-    <t>0.5404,0.3280,0.2041,0.0086</t>
-  </si>
-  <si>
-    <t>0.0081,0.0280,0.9870,0.0034</t>
-  </si>
-  <si>
-    <t>0.0108,0.9612,0.0475,0.0002</t>
-  </si>
-  <si>
-    <t>0.9159,0.0499,0.0142,0.0099</t>
-  </si>
-  <si>
-    <t>0.8742,0.1597,0.0101,0.0015</t>
-  </si>
-  <si>
-    <t>0.5538,0.5444,0.0194,0.0020</t>
-  </si>
-  <si>
-    <t>0.0201,0.9456,0.2081,0.0014</t>
-  </si>
-  <si>
-    <t>0.0095,0.8878,0.3722,0.0049</t>
-  </si>
-  <si>
-    <t>0.0344,0.0445,0.9039,0.0519</t>
-  </si>
-  <si>
-    <t>0.0742,0.1200,0.8519,0.0341</t>
-  </si>
-  <si>
-    <t>0.0933,0.0068,0.8932,0.0296</t>
-  </si>
-  <si>
-    <t>0.0140,0.1740,0.9538,0.0027</t>
-  </si>
-  <si>
-    <t>0.0121,0.9732,0.0162,0.0001</t>
-  </si>
-  <si>
-    <t>0.0113,0.0687,0.9465,0.0210</t>
-  </si>
-  <si>
-    <t>0.2295,0.5052,0.0566,0.7206</t>
-  </si>
-  <si>
-    <t>0.0015,0.9907,0.0042,0.0045</t>
-  </si>
-  <si>
-    <t>0.0013,0.9894,0.0237,0.0029</t>
-  </si>
-  <si>
-    <t>0.0020,0.9872,0.0054,0.0052</t>
-  </si>
-  <si>
-    <t>0.0376,0.3913,0.8341,0.0092</t>
-  </si>
-  <si>
-    <t>0.0339,0.1292,0.9326,0.0117</t>
-  </si>
-  <si>
-    <t>0.0718,0.0833,0.8777,0.0070</t>
-  </si>
-  <si>
-    <t>0.3041,0.0038,0.8579,0.0024</t>
-  </si>
-  <si>
-    <t>0.0224,0.0147,0.9751,0.0047</t>
-  </si>
-  <si>
-    <t>0.0174,0.0532,0.9691,0.0009</t>
-  </si>
-  <si>
-    <t>0.9670,0.0469,0.0017,0.0009</t>
-  </si>
-  <si>
-    <t>0.9747,0.0219,0.0056,0.0007</t>
-  </si>
-  <si>
-    <t>0.9722,0.0316,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.0088,0.4751,0.9580,0.0006</t>
-  </si>
-  <si>
-    <t>0.9851,0.0159,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9803,0.0297,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9025,0.1492,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.0026,0.2547,0.9817,0.0010</t>
-  </si>
-  <si>
-    <t>0.0077,0.4020,0.9616,0.0018</t>
-  </si>
-  <si>
-    <t>0.0033,0.0082,0.9601,0.0728</t>
-  </si>
-  <si>
-    <t>0.0007,0.9337,0.9006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0154,0.0153,0.9837,0.0013</t>
-  </si>
-  <si>
-    <t>0.0279,0.8931,0.1470,0.0003</t>
-  </si>
-  <si>
-    <t>0.0054,0.9930,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.8860,0.0898,0.0293,0.0026</t>
-  </si>
-  <si>
-    <t>0.5965,0.2979,0.1847,0.0117</t>
-  </si>
-  <si>
-    <t>0.0079,0.0446,0.9836,0.0015</t>
-  </si>
-  <si>
-    <t>0.0023,0.9819,0.1516,0.0002</t>
-  </si>
-  <si>
-    <t>0.0046,0.8805,0.7019,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.9800,0.2250,0.0003</t>
-  </si>
-  <si>
-    <t>0.0043,0.8680,0.8394,0.0005</t>
-  </si>
-  <si>
-    <t>0.0192,0.0029,0.0102,0.9819</t>
-  </si>
-  <si>
-    <t>0.0015,0.1250,0.0001,0.9976</t>
-  </si>
-  <si>
-    <t>0.0031,0.0255,0.0004,0.9975</t>
-  </si>
-  <si>
-    <t>0.0283,0.0055,0.0017,0.9869</t>
-  </si>
-  <si>
-    <t>0.0254,0.0137,0.0025,0.9875</t>
-  </si>
-  <si>
-    <t>0.0503,0.0167,0.0035,0.9781</t>
-  </si>
-  <si>
-    <t>0.0007,0.9855,0.4928,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.8543,0.9499,0.0001</t>
-  </si>
-  <si>
-    <t>0.0346,0.6354,0.6464,0.0035</t>
-  </si>
-  <si>
-    <t>0.0040,0.7035,0.9516,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9597,0.5907,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.9814,0.3315,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0018,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9471,0.0879,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9873,0.0112,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9859,0.0137,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9910,0.0091,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.8668,0.1880,0.0073,0.0005</t>
-  </si>
-  <si>
-    <t>0.9944,0.0025,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9810,0.0289,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0040,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0079,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9954,0.0025,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0054,0.0027,0.9823,0.0174</t>
-  </si>
-  <si>
-    <t>0.0946,0.0251,0.9090,0.0129</t>
-  </si>
-  <si>
-    <t>0.7675,0.0182,0.1332,0.0414</t>
-  </si>
-  <si>
-    <t>0.0350,0.0074,0.9699,0.0014</t>
-  </si>
-  <si>
-    <t>0.0798,0.9344,0.0040,0.0006</t>
-  </si>
-  <si>
-    <t>0.0285,0.9793,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.1361,0.8988,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.0304,0.9675,0.0066,0.0002</t>
-  </si>
-  <si>
-    <t>0.0360,0.9690,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0303,0.9757,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.7080,0.4467,0.0048,0.0006</t>
-  </si>
-  <si>
-    <t>0.5471,0.1570,0.3544,0.0676</t>
-  </si>
-  <si>
-    <t>0.2709,0.0041,0.8202,0.0177</t>
-  </si>
-  <si>
-    <t>0.7680,0.0617,0.1702,0.0053</t>
-  </si>
-  <si>
-    <t>0.6020,0.1306,0.3026,0.0122</t>
-  </si>
-  <si>
-    <t>0.3403,0.1106,0.1673,0.5659</t>
-  </si>
-  <si>
-    <t>0.0006,0.9949,0.0041,0.0020</t>
-  </si>
-  <si>
-    <t>0.0029,0.9884,0.0141,0.0012</t>
-  </si>
-  <si>
-    <t>0.2575,0.6693,0.0623,0.0678</t>
-  </si>
-  <si>
-    <t>0.0041,0.9468,0.6188,0.0007</t>
-  </si>
-  <si>
-    <t>0.0078,0.9786,0.1059,0.0001</t>
-  </si>
-  <si>
-    <t>0.7087,0.3211,0.0294,0.0038</t>
-  </si>
-  <si>
-    <t>0.6601,0.3837,0.0310,0.0004</t>
-  </si>
-  <si>
-    <t>0.9183,0.1007,0.0068,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0008,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9960,0.0009,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9801,0.0127,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.9938,0.0028,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9788,0.0085,0.0100,0.0009</t>
-  </si>
-  <si>
-    <t>0.9897,0.0077,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0101,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.0081,0.5829,0.9165,0.0010</t>
-  </si>
-  <si>
-    <t>0.0068,0.7589,0.8519,0.0007</t>
-  </si>
-  <si>
-    <t>0.0218,0.2633,0.9156,0.0014</t>
-  </si>
-  <si>
-    <t>0.0417,0.2273,0.8758,0.0054</t>
-  </si>
-  <si>
-    <t>0.7808,0.1694,0.0543,0.0058</t>
-  </si>
-  <si>
-    <t>0.7548,0.1219,0.1113,0.0125</t>
-  </si>
-  <si>
-    <t>0.4101,0.0099,0.7361,0.0093</t>
-  </si>
-  <si>
-    <t>0.7691,0.0456,0.2232,0.0055</t>
-  </si>
-  <si>
-    <t>0.1419,0.0016,0.0020,0.9509</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.0038,0.9970</t>
-  </si>
-  <si>
-    <t>0.0176,0.0048,0.0017,0.9906</t>
-  </si>
-  <si>
-    <t>0.0373,0.0032,0.0034,0.9834</t>
-  </si>
-  <si>
-    <t>0.0028,0.9086,0.6389,0.0076</t>
-  </si>
-  <si>
-    <t>0.9797,0.0255,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.4012,0.7163,0.0053,0.0065</t>
-  </si>
-  <si>
-    <t>0.9830,0.0106,0.0023,0.0016</t>
-  </si>
-  <si>
-    <t>0.1295,0.8885,0.0124,0.0009</t>
-  </si>
-  <si>
-    <t>0.9740,0.0007,0.0006,0.0250</t>
-  </si>
-  <si>
-    <t>0.0704,0.0019,0.0018,0.9768</t>
-  </si>
-  <si>
-    <t>0.9906,0.0031,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.0225,0.0601,0.9108,0.0810</t>
-  </si>
-  <si>
-    <t>0.5250,0.0001,0.0045,0.6101</t>
-  </si>
-  <si>
-    <t>0.9416,0.0017,0.0015,0.0521</t>
-  </si>
-  <si>
-    <t>0.3709,0.6361,0.0088,0.0138</t>
-  </si>
-  <si>
-    <t>0.8622,0.1441,0.0132,0.0007</t>
-  </si>
-  <si>
-    <t>0.9593,0.0150,0.0201,0.0015</t>
-  </si>
-  <si>
-    <t>0.1429,0.8451,0.0118,0.0019</t>
-  </si>
-  <si>
-    <t>0.7365,0.1208,0.1714,0.0080</t>
-  </si>
-  <si>
-    <t>0.7827,0.1221,0.0925,0.0013</t>
-  </si>
-  <si>
-    <t>0.9887,0.0080,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9945,0.0020,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9917,0.0030,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.9660,0.0240,0.0080,0.0044</t>
-  </si>
-  <si>
-    <t>0.9824,0.0213,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9904,0.0081,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0028,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9844,0.0136,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.5185,0.6418,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.4963,0.6614,0.0068,0.0011</t>
-  </si>
-  <si>
-    <t>0.6167,0.5573,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.6768,0.2470,0.1167,0.0253</t>
-  </si>
-  <si>
-    <t>0.9782,0.0272,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9519,0.0395,0.0055,0.0023</t>
-  </si>
-  <si>
-    <t>0.9510,0.0657,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.9199,0.1116,0.0028,0.0016</t>
-  </si>
-  <si>
-    <t>0.0062,0.0373,0.9902,0.0012</t>
-  </si>
-  <si>
-    <t>0.9356,0.0792,0.0055,0.0015</t>
-  </si>
-  <si>
-    <t>0.0160,0.0069,0.9879,0.0012</t>
-  </si>
-  <si>
-    <t>0.0103,0.2078,0.9656,0.0041</t>
-  </si>
-  <si>
-    <t>0.0298,0.0367,0.9576,0.0031</t>
-  </si>
-  <si>
-    <t>0.0122,0.3007,0.9530,0.0015</t>
-  </si>
-  <si>
-    <t>0.0195,0.0097,0.9830,0.0009</t>
-  </si>
-  <si>
-    <t>0.0092,0.0115,0.9900,0.0008</t>
-  </si>
-  <si>
-    <t>0.0162,0.0973,0.9535,0.0006</t>
-  </si>
-  <si>
-    <t>0.3510,0.1168,0.5194,0.0780</t>
-  </si>
-  <si>
-    <t>0.4148,0.0638,0.6697,0.0066</t>
-  </si>
-  <si>
-    <t>0.6124,0.1578,0.2428,0.0087</t>
-  </si>
-  <si>
-    <t>0.2950,0.5508,0.2099,0.0181</t>
-  </si>
-  <si>
-    <t>0.3925,0.1845,0.4228,0.0027</t>
-  </si>
-  <si>
-    <t>0.6863,0.0928,0.1774,0.0006</t>
-  </si>
-  <si>
-    <t>0.4330,0.2131,0.3479,0.0049</t>
-  </si>
-  <si>
-    <t>0.4849,0.0996,0.4880,0.0041</t>
-  </si>
-  <si>
-    <t>0.8225,0.2566,0.0067,0.0006</t>
-  </si>
-  <si>
-    <t>0.8070,0.3039,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.7922,0.3829,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9752,0.0281,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.4118,0.7445,0.0036,0.0014</t>
-  </si>
-  <si>
-    <t>0.6509,0.0128,0.5449,0.0020</t>
-  </si>
-  <si>
-    <t>0.7590,0.0484,0.2503,0.0105</t>
-  </si>
-  <si>
-    <t>0.7503,0.0554,0.1953,0.0247</t>
-  </si>
-  <si>
-    <t>0.7727,0.0150,0.2869,0.0125</t>
-  </si>
-  <si>
-    <t>0.7352,0.0334,0.2653,0.0131</t>
-  </si>
-  <si>
-    <t>0.0113,0.0147,0.9810,0.0066</t>
-  </si>
-  <si>
-    <t>0.0483,0.6472,0.7172,0.0153</t>
-  </si>
-  <si>
-    <t>0.0589,0.0782,0.9050,0.0164</t>
-  </si>
-  <si>
-    <t>0.1392,0.0855,0.8424,0.0069</t>
-  </si>
-  <si>
-    <t>0.0352,0.4170,0.7772,0.0241</t>
-  </si>
-  <si>
-    <t>0.9857,0.0074,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.9840,0.0169,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9909,0.0049,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9914,0.0109,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9652,0.0425,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9829,0.0189,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9954,0.0032,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0009,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0964,0.0207,0.9452,0.0022</t>
-  </si>
-  <si>
-    <t>0.2817,0.5133,0.3483,0.0221</t>
-  </si>
-  <si>
-    <t>0.9407,0.0339,0.0165,0.0042</t>
-  </si>
-  <si>
-    <t>0.0123,0.0095,0.9869,0.0012</t>
-  </si>
-  <si>
-    <t>0.0010,0.0135,0.9901,0.0078</t>
-  </si>
-  <si>
-    <t>0.0193,0.0142,0.9748,0.0009</t>
-  </si>
-  <si>
-    <t>0.0018,0.0074,0.9932,0.0043</t>
-  </si>
-  <si>
-    <t>0.0740,0.2196,0.7652,0.0336</t>
-  </si>
-  <si>
-    <t>0.0027,0.0038,0.9880,0.0138</t>
-  </si>
-  <si>
-    <t>0.0179,0.0338,0.9629,0.0019</t>
-  </si>
-  <si>
-    <t>0.0693,0.2769,0.7899,0.0044</t>
-  </si>
-  <si>
-    <t>0.7116,0.0344,0.3281,0.0268</t>
-  </si>
-  <si>
-    <t>0.8363,0.0054,0.2661,0.0022</t>
-  </si>
-  <si>
-    <t>0.8587,0.0123,0.1431,0.0085</t>
-  </si>
-  <si>
-    <t>0.9876,0.0127,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9942,0.0050,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9801,0.0306,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9928,0.0013,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9335,0.1153,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9873,0.0187,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0076,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0467,0.1269,0.8515,0.0059</t>
-  </si>
-  <si>
-    <t>0.0187,0.0993,0.9669,0.0018</t>
-  </si>
-  <si>
-    <t>0.0042,0.2118,0.9636,0.0012</t>
-  </si>
-  <si>
-    <t>0.0445,0.0128,0.9509,0.0038</t>
-  </si>
-  <si>
-    <t>0.0193,0.0087,0.9739,0.0024</t>
-  </si>
-  <si>
-    <t>0.3344,0.0124,0.2944,0.4406</t>
-  </si>
-  <si>
-    <t>0.0402,0.0585,0.9312,0.0089</t>
-  </si>
-  <si>
-    <t>0.0351,0.1237,0.7650,0.1328</t>
-  </si>
-  <si>
-    <t>0.8830,0.0006,0.0034,0.1339</t>
-  </si>
-  <si>
-    <t>0.0028,0.0826,0.0010,0.9958</t>
-  </si>
-  <si>
-    <t>0.0308,0.0393,0.0010,0.9846</t>
-  </si>
-  <si>
-    <t>0.0085,0.0002,0.0003,0.9972</t>
-  </si>
-  <si>
-    <t>0.0053,0.0002,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.3841,0.0049,0.0664,0.6388</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9382,0.0130,0.0083,0.0159</t>
+  </si>
+  <si>
+    <t>0.0517,0.0005,0.0012,0.9830</t>
+  </si>
+  <si>
+    <t>0.9053,0.0178,0.0061,0.0520</t>
+  </si>
+  <si>
+    <t>0.2078,0.0041,0.0049,0.9119</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0039,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9915,0.0108,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9926,0.0102,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9931,0.0101,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.2327,0.5607,0.2930,0.0127</t>
+  </si>
+  <si>
+    <t>0.1530,0.5266,0.3927,0.0504</t>
+  </si>
+  <si>
+    <t>0.6824,0.0207,0.4588,0.0007</t>
+  </si>
+  <si>
+    <t>0.0667,0.0357,0.8963,0.0212</t>
+  </si>
+  <si>
+    <t>0.7678,0.0108,0.2009,0.0530</t>
+  </si>
+  <si>
+    <t>0.0131,0.9762,0.0164,0.0005</t>
+  </si>
+  <si>
+    <t>0.0063,0.9922,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.1762,0.8712,0.0056,0.0011</t>
+  </si>
+  <si>
+    <t>0.0227,0.9666,0.0186,0.0003</t>
+  </si>
+  <si>
+    <t>0.0039,0.9886,0.0293,0.0000</t>
+  </si>
+  <si>
+    <t>0.5323,0.0103,0.5722,0.0105</t>
+  </si>
+  <si>
+    <t>0.6148,0.0249,0.3540,0.0487</t>
+  </si>
+  <si>
+    <t>0.0252,0.0042,0.9860,0.0007</t>
+  </si>
+  <si>
+    <t>0.3674,0.0110,0.7615,0.0061</t>
+  </si>
+  <si>
+    <t>0.0248,0.0045,0.9830,0.0014</t>
+  </si>
+  <si>
+    <t>0.2097,0.0033,0.8772,0.0082</t>
+  </si>
+  <si>
+    <t>0.0049,0.0068,0.9857,0.0116</t>
+  </si>
+  <si>
+    <t>0.1690,0.8525,0.0142,0.0008</t>
+  </si>
+  <si>
+    <t>0.2953,0.5027,0.2323,0.0072</t>
+  </si>
+  <si>
+    <t>0.0084,0.1345,0.9723,0.0032</t>
+  </si>
+  <si>
+    <t>0.0050,0.8605,0.7358,0.0007</t>
+  </si>
+  <si>
+    <t>0.7857,0.2405,0.0161,0.0025</t>
+  </si>
+  <si>
+    <t>0.5064,0.0876,0.4262,0.0077</t>
+  </si>
+  <si>
+    <t>0.5040,0.6453,0.0077,0.0007</t>
+  </si>
+  <si>
+    <t>0.0493,0.9083,0.1727,0.0039</t>
+  </si>
+  <si>
+    <t>0.0535,0.6760,0.4088,0.0048</t>
+  </si>
+  <si>
+    <t>0.0787,0.1497,0.7720,0.0812</t>
+  </si>
+  <si>
+    <t>0.0368,0.4436,0.7377,0.0068</t>
+  </si>
+  <si>
+    <t>0.0870,0.0103,0.8134,0.0928</t>
+  </si>
+  <si>
+    <t>0.0216,0.2666,0.9171,0.0024</t>
+  </si>
+  <si>
+    <t>0.0021,0.9909,0.0092,0.0001</t>
+  </si>
+  <si>
+    <t>0.0098,0.0167,0.9431,0.0509</t>
+  </si>
+  <si>
+    <t>0.0326,0.1035,0.0016,0.9743</t>
+  </si>
+  <si>
+    <t>0.0028,0.9888,0.0068,0.0009</t>
+  </si>
+  <si>
+    <t>0.0034,0.9794,0.0760,0.0016</t>
+  </si>
+  <si>
+    <t>0.0011,0.9890,0.0193,0.0054</t>
+  </si>
+  <si>
+    <t>0.0209,0.1523,0.8827,0.0266</t>
+  </si>
+  <si>
+    <t>0.0022,0.7326,0.9545,0.0005</t>
+  </si>
+  <si>
+    <t>0.1757,0.1968,0.7164,0.0068</t>
+  </si>
+  <si>
+    <t>0.0115,0.0031,0.9900,0.0009</t>
+  </si>
+  <si>
+    <t>0.0078,0.0632,0.9847,0.0007</t>
+  </si>
+  <si>
+    <t>0.0691,0.4700,0.5122,0.0015</t>
+  </si>
+  <si>
+    <t>0.6719,0.4613,0.0016,0.0024</t>
+  </si>
+  <si>
+    <t>0.9510,0.0434,0.0121,0.0006</t>
+  </si>
+  <si>
+    <t>0.8601,0.1388,0.0256,0.0032</t>
+  </si>
+  <si>
+    <t>0.0130,0.0636,0.9783,0.0058</t>
+  </si>
+  <si>
+    <t>0.9819,0.0226,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9329,0.1144,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9245,0.9136,0.0003</t>
+  </si>
+  <si>
+    <t>0.0049,0.7045,0.7887,0.0005</t>
+  </si>
+  <si>
+    <t>0.0146,0.0569,0.9691,0.0045</t>
+  </si>
+  <si>
+    <t>0.0055,0.7175,0.8762,0.0023</t>
+  </si>
+  <si>
+    <t>0.0029,0.0037,0.9925,0.0035</t>
+  </si>
+  <si>
+    <t>0.0260,0.9413,0.0396,0.0001</t>
+  </si>
+  <si>
+    <t>0.0102,0.9852,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.8553,0.0180,0.1849,0.0042</t>
+  </si>
+  <si>
+    <t>0.6753,0.2216,0.1477,0.0123</t>
+  </si>
+  <si>
+    <t>0.0348,0.1701,0.9320,0.0035</t>
+  </si>
+  <si>
+    <t>0.0025,0.9668,0.3380,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9519,0.7671,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9937,0.0915,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.9495,0.6147,0.0005</t>
+  </si>
+  <si>
+    <t>0.0584,0.0050,0.0141,0.9639</t>
+  </si>
+  <si>
+    <t>0.0047,0.0332,0.0001,0.9971</t>
+  </si>
+  <si>
+    <t>0.0061,0.0032,0.0005,0.9967</t>
+  </si>
+  <si>
+    <t>0.0364,0.0009,0.0003,0.9907</t>
+  </si>
+  <si>
+    <t>0.0142,0.0055,0.0029,0.9921</t>
+  </si>
+  <si>
+    <t>0.0704,0.0125,0.0024,0.9697</t>
+  </si>
+  <si>
+    <t>0.0003,0.9522,0.9261,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.4203,0.9287,0.0001</t>
+  </si>
+  <si>
+    <t>0.0141,0.7266,0.8167,0.0041</t>
+  </si>
+  <si>
+    <t>0.0074,0.6950,0.8801,0.0026</t>
+  </si>
+  <si>
+    <t>0.0009,0.9655,0.8207,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9884,0.3319,0.0002</t>
+  </si>
+  <si>
+    <t>0.9911,0.0074,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9832,0.0225,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9661,0.0381,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9186,0.1270,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9861,0.0150,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9527,0.0750,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9954,0.0036,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0041,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9890,0.0100,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0024,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.0011,0.9943,0.0022</t>
+  </si>
+  <si>
+    <t>0.0748,0.0345,0.9198,0.0015</t>
+  </si>
+  <si>
+    <t>0.7722,0.0172,0.2264,0.0111</t>
+  </si>
+  <si>
+    <t>0.0411,0.0101,0.9698,0.0007</t>
+  </si>
+  <si>
+    <t>0.0941,0.9324,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.2228,0.8524,0.0041,0.0001</t>
+  </si>
+  <si>
+    <t>0.0258,0.9716,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.3053,0.7976,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.0918,0.9305,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.0180,0.9805,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.1862,0.8232,0.0231,0.0015</t>
+  </si>
+  <si>
+    <t>0.6088,0.1479,0.3055,0.0293</t>
+  </si>
+  <si>
+    <t>0.0900,0.0057,0.9356,0.0081</t>
+  </si>
+  <si>
+    <t>0.7358,0.0609,0.2096,0.0046</t>
+  </si>
+  <si>
+    <t>0.5932,0.0859,0.3508,0.0030</t>
+  </si>
+  <si>
+    <t>0.0520,0.0736,0.0214,0.9474</t>
+  </si>
+  <si>
+    <t>0.0006,0.9966,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.9898,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.0698,0.8838,0.0344,0.0115</t>
+  </si>
+  <si>
+    <t>0.0004,0.9711,0.9107,0.0000</t>
+  </si>
+  <si>
+    <t>0.0143,0.9747,0.0278,0.0002</t>
+  </si>
+  <si>
+    <t>0.8538,0.1759,0.0151,0.0005</t>
+  </si>
+  <si>
+    <t>0.4101,0.6213,0.0257,0.0007</t>
+  </si>
+  <si>
+    <t>0.9846,0.0180,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0009,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9889,0.0022,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9733,0.0198,0.0040,0.0019</t>
+  </si>
+  <si>
+    <t>0.9942,0.0044,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9239,0.0662,0.0274,0.0021</t>
+  </si>
+  <si>
+    <t>0.9829,0.0110,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9926,0.0023,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0051,0.7168,0.8874,0.0006</t>
+  </si>
+  <si>
+    <t>0.0238,0.5816,0.7447,0.0010</t>
+  </si>
+  <si>
+    <t>0.0082,0.7908,0.6894,0.0009</t>
+  </si>
+  <si>
+    <t>0.0607,0.0535,0.9176,0.0135</t>
+  </si>
+  <si>
+    <t>0.9088,0.0452,0.0188,0.0035</t>
+  </si>
+  <si>
+    <t>0.8228,0.0083,0.2558,0.0030</t>
+  </si>
+  <si>
+    <t>0.3853,0.0055,0.7692,0.0129</t>
+  </si>
+  <si>
+    <t>0.6938,0.0564,0.1511,0.0712</t>
+  </si>
+  <si>
+    <t>0.1901,0.0106,0.0076,0.9076</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0004,0.9990</t>
+  </si>
+  <si>
+    <t>0.0030,0.0067,0.0011,0.9973</t>
+  </si>
+  <si>
+    <t>0.0110,0.0003,0.0021,0.9940</t>
+  </si>
+  <si>
+    <t>0.0009,0.9793,0.1772,0.0018</t>
+  </si>
+  <si>
+    <t>0.9455,0.0625,0.0060,0.0008</t>
+  </si>
+  <si>
+    <t>0.2899,0.8306,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.9888,0.0030,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.3776,0.7292,0.0090,0.0014</t>
+  </si>
+  <si>
+    <t>0.9855,0.0015,0.0007,0.0065</t>
+  </si>
+  <si>
+    <t>0.4064,0.0059,0.0172,0.7363</t>
+  </si>
+  <si>
+    <t>0.9779,0.0090,0.0019,0.0043</t>
+  </si>
+  <si>
+    <t>0.0780,0.1358,0.8586,0.0435</t>
+  </si>
+  <si>
+    <t>0.3118,0.0019,0.0031,0.8477</t>
+  </si>
+  <si>
+    <t>0.9573,0.0044,0.0122,0.0092</t>
+  </si>
+  <si>
+    <t>0.4865,0.5319,0.0312,0.0088</t>
+  </si>
+  <si>
+    <t>0.8000,0.2400,0.0120,0.0012</t>
+  </si>
+  <si>
+    <t>0.9405,0.0429,0.0119,0.0014</t>
+  </si>
+  <si>
+    <t>0.1936,0.8002,0.0174,0.0063</t>
+  </si>
+  <si>
+    <t>0.8691,0.0969,0.0318,0.0004</t>
+  </si>
+  <si>
+    <t>0.8939,0.0401,0.0506,0.0079</t>
+  </si>
+  <si>
+    <t>0.9965,0.0016,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9903,0.0095,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9837,0.0113,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.9803,0.0096,0.0033,0.0023</t>
+  </si>
+  <si>
+    <t>0.9961,0.0022,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9935,0.0040,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0014,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0015,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.5501,0.5448,0.0157,0.0015</t>
+  </si>
+  <si>
+    <t>0.4860,0.6922,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.3514,0.7896,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.6166,0.3318,0.1313,0.0237</t>
+  </si>
+  <si>
+    <t>0.4539,0.6958,0.0022,0.0015</t>
+  </si>
+  <si>
+    <t>0.4981,0.5467,0.0413,0.0036</t>
+  </si>
+  <si>
+    <t>0.9586,0.0837,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.6795,0.5254,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.0236,0.0910,0.9660,0.0020</t>
+  </si>
+  <si>
+    <t>0.9156,0.0658,0.0302,0.0010</t>
+  </si>
+  <si>
+    <t>0.0022,0.0084,0.9958,0.0010</t>
+  </si>
+  <si>
+    <t>0.0069,0.0869,0.9800,0.0029</t>
+  </si>
+  <si>
+    <t>0.3655,0.0078,0.7782,0.0045</t>
+  </si>
+  <si>
+    <t>0.0718,0.0209,0.9372,0.0024</t>
+  </si>
+  <si>
+    <t>0.0261,0.0149,0.9753,0.0011</t>
+  </si>
+  <si>
+    <t>0.0575,0.0004,0.9773,0.0004</t>
+  </si>
+  <si>
+    <t>0.0229,0.0081,0.9725,0.0042</t>
+  </si>
+  <si>
+    <t>0.3058,0.1359,0.6034,0.0714</t>
+  </si>
+  <si>
+    <t>0.2801,0.1154,0.6600,0.0095</t>
+  </si>
+  <si>
+    <t>0.2974,0.2638,0.4563,0.0065</t>
+  </si>
+  <si>
+    <t>0.3300,0.0755,0.6988,0.0034</t>
+  </si>
+  <si>
+    <t>0.1399,0.1051,0.8193,0.0049</t>
+  </si>
+  <si>
+    <t>0.4390,0.2063,0.3065,0.0028</t>
+  </si>
+  <si>
+    <t>0.5230,0.2259,0.3002,0.0112</t>
+  </si>
+  <si>
+    <t>0.5315,0.2210,0.2833,0.0434</t>
+  </si>
+  <si>
+    <t>0.7002,0.4540,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.3448,0.7471,0.0104,0.0003</t>
+  </si>
+  <si>
+    <t>0.1988,0.8403,0.0122,0.0014</t>
+  </si>
+  <si>
+    <t>0.9834,0.0223,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.1521,0.8930,0.0048,0.0012</t>
+  </si>
+  <si>
+    <t>0.4694,0.3103,0.2959,0.0321</t>
+  </si>
+  <si>
+    <t>0.7236,0.0598,0.2925,0.0090</t>
+  </si>
+  <si>
+    <t>0.9204,0.0043,0.0238,0.0134</t>
+  </si>
+  <si>
+    <t>0.7733,0.0209,0.2524,0.0066</t>
+  </si>
+  <si>
+    <t>0.8291,0.0200,0.1839,0.0047</t>
+  </si>
+  <si>
+    <t>0.0097,0.0127,0.9813,0.0074</t>
+  </si>
+  <si>
+    <t>0.0322,0.0285,0.9455,0.0153</t>
+  </si>
+  <si>
+    <t>0.0943,0.0728,0.8878,0.0190</t>
+  </si>
+  <si>
+    <t>0.0862,0.1245,0.8327,0.0209</t>
+  </si>
+  <si>
+    <t>0.0273,0.3231,0.8949,0.0127</t>
+  </si>
+  <si>
+    <t>0.8887,0.1524,0.0072,0.0007</t>
+  </si>
+  <si>
+    <t>0.9597,0.0520,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.9587,0.0631,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9788,0.0389,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9887,0.0120,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9860,0.0146,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0043,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9821,0.0192,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.2029,0.0665,0.8666,0.0040</t>
+  </si>
+  <si>
+    <t>0.6183,0.2453,0.2359,0.0224</t>
+  </si>
+  <si>
+    <t>0.8837,0.0876,0.0096,0.0183</t>
+  </si>
+  <si>
+    <t>0.0356,0.3389,0.8153,0.0049</t>
+  </si>
+  <si>
+    <t>0.0019,0.0336,0.9910,0.0023</t>
+  </si>
+  <si>
+    <t>0.0156,0.0458,0.9690,0.0044</t>
+  </si>
+  <si>
+    <t>0.0034,0.0025,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.1077,0.0149,0.9053,0.0108</t>
+  </si>
+  <si>
+    <t>0.0038,0.0171,0.9933,0.0014</t>
+  </si>
+  <si>
+    <t>0.0079,0.0357,0.9743,0.0041</t>
+  </si>
+  <si>
+    <t>0.0783,0.1165,0.8522,0.0211</t>
+  </si>
+  <si>
+    <t>0.8731,0.0014,0.2296,0.0019</t>
+  </si>
+  <si>
+    <t>0.7610,0.0116,0.3721,0.0072</t>
+  </si>
+  <si>
+    <t>0.7453,0.0065,0.4351,0.0040</t>
+  </si>
+  <si>
+    <t>0.9942,0.0070,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9745,0.0385,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0030,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9836,0.0200,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0019,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9805,0.0228,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9863,0.0124,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9941,0.0043,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0730,0.0277,0.9315,0.0011</t>
+  </si>
+  <si>
+    <t>0.0024,0.4451,0.9557,0.0015</t>
+  </si>
+  <si>
+    <t>0.0112,0.1248,0.9483,0.0084</t>
+  </si>
+  <si>
+    <t>0.1382,0.1170,0.7705,0.0057</t>
+  </si>
+  <si>
+    <t>0.0112,0.0026,0.9872,0.0027</t>
+  </si>
+  <si>
+    <t>0.3756,0.0058,0.5875,0.0781</t>
+  </si>
+  <si>
+    <t>0.3364,0.0506,0.6630,0.0427</t>
+  </si>
+  <si>
+    <t>0.0207,0.0404,0.9147,0.0722</t>
+  </si>
+  <si>
+    <t>0.4142,0.0004,0.0009,0.8513</t>
+  </si>
+  <si>
+    <t>0.0144,0.0438,0.0011,0.9915</t>
+  </si>
+  <si>
+    <t>0.0612,0.0013,0.0002,0.9852</t>
+  </si>
+  <si>
+    <t>0.0103,0.0017,0.0007,0.9953</t>
+  </si>
+  <si>
+    <t>0.0083,0.0006,0.0020,0.9933</t>
+  </si>
+  <si>
+    <t>0.6470,0.0520,0.0549,0.2368</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,10 +2830,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,10 +4412,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,10 +4426,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
